--- a/PV_ICE/baselines/SupportingMaterial/Manual Files/inverter_Sector_deployment_inverterpm2.xlsx
+++ b/PV_ICE/baselines/SupportingMaterial/Manual Files/inverter_Sector_deployment_inverterpm2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\Manual Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67206490-E3AA-455E-A1F5-CACF831A305C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063B8D61-9095-44DA-8508-2E3471BE23B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B6A43E6F-DE9F-4A36-BCD0-E8AF60DFB633}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="31">
   <si>
     <t>Inverter type deployed</t>
   </si>
@@ -99,6 +99,36 @@
   </si>
   <si>
     <t>year</t>
+  </si>
+  <si>
+    <t>107 GWac</t>
+  </si>
+  <si>
+    <t>129 GWac</t>
+  </si>
+  <si>
+    <t>185 GWac</t>
+  </si>
+  <si>
+    <t>223 GWac</t>
+  </si>
+  <si>
+    <t>344 GWac</t>
+  </si>
+  <si>
+    <t>536 GWac</t>
+  </si>
+  <si>
+    <t>utiltiy scale = &gt;150 kWac</t>
+  </si>
+  <si>
+    <t>Total Shipments</t>
+  </si>
+  <si>
+    <t>GLOBAL SHIPMENTS</t>
+  </si>
+  <si>
+    <t>USA</t>
   </si>
 </sst>
 </file>
@@ -151,21 +181,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9EC8D6-0CFC-4885-9077-B7BCF4C9AF4B}">
-  <dimension ref="A1:N112"/>
+  <dimension ref="A1:AH113"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.81640625" bestFit="1" customWidth="1"/>
@@ -510,857 +541,1110 @@
     <col min="9" max="9" width="6.6328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2.26953125" customWidth="1"/>
+    <col min="25" max="25" width="1.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="P1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2">
+      <c r="N2" s="1"/>
+      <c r="P2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>1990</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>1991</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>1992</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>1993</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>1994</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>1995</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>1996</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A10">
         <v>1997</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A11">
         <v>1998</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A12">
         <v>1999</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>2001</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A15">
         <v>2002</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>2003</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>2004</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>2005</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>2006</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A20">
         <v>2007</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A21">
         <v>2008</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A22">
         <v>2009</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A23">
         <v>2010</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A24">
         <v>2011</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A25">
         <v>2012</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A26">
         <v>2013</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A27">
         <v>2014</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A28">
         <v>2015</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A29">
         <v>2016</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C29" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="4" t="s">
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G29" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="3"/>
-      <c r="I28" s="4" t="s">
+      <c r="H29" s="7"/>
+      <c r="I29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A30">
         <v>2017</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>9</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" t="s">
         <v>10</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>11</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E30" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="2"/>
-      <c r="G29" t="s">
+      <c r="F30" s="2"/>
+      <c r="G30" t="s">
         <v>13</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H30" t="s">
         <v>14</v>
       </c>
-      <c r="I29" s="2"/>
-      <c r="J29" t="s">
+      <c r="I30" s="2"/>
+      <c r="J30" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A31">
         <v>2018</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B31" s="4">
         <v>5915</v>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>841</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D31" s="4">
         <v>1971</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E31" s="4">
         <v>1876</v>
       </c>
-      <c r="F30" s="6">
-        <f>SUM(C30:E30)</f>
+      <c r="F31" s="5">
+        <f>SUM(C31:E31)</f>
         <v>4688</v>
       </c>
-      <c r="G30">
+      <c r="G31">
         <v>751</v>
       </c>
-      <c r="H30">
+      <c r="H31">
         <v>154</v>
       </c>
-      <c r="I30" s="2">
-        <f>SUM(G30:H30)</f>
+      <c r="I31" s="2">
+        <f>SUM(G31:H31)</f>
         <v>905</v>
       </c>
-      <c r="J30" s="5">
+      <c r="J31" s="4">
         <v>11508</v>
       </c>
-      <c r="K30" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>2019</v>
-      </c>
-      <c r="B31" s="5">
-        <v>11318</v>
-      </c>
-      <c r="C31">
-        <v>972</v>
-      </c>
-      <c r="D31" s="5">
-        <v>2289</v>
-      </c>
-      <c r="E31" s="5">
-        <v>2277</v>
-      </c>
-      <c r="F31" s="6">
-        <f t="shared" ref="F31:F35" si="0">SUM(C31:E31)</f>
-        <v>5538</v>
-      </c>
-      <c r="G31" s="5">
-        <v>1489</v>
-      </c>
-      <c r="H31">
-        <v>124</v>
-      </c>
-      <c r="I31" s="2">
-        <f t="shared" ref="I31:I35" si="1">SUM(G31:H31)</f>
-        <v>1613</v>
-      </c>
-      <c r="J31" s="5">
-        <v>18470</v>
-      </c>
-      <c r="K31" s="5" t="s">
+      <c r="K31" s="4" t="s">
         <v>16</v>
       </c>
       <c r="L31" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="V31" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z31" s="4">
+        <v>5915</v>
+      </c>
+      <c r="AA31">
+        <v>841</v>
+      </c>
+      <c r="AB31" s="4">
+        <v>1971</v>
+      </c>
+      <c r="AC31" s="4">
+        <v>1876</v>
+      </c>
+      <c r="AD31">
+        <v>751</v>
+      </c>
+      <c r="AE31">
+        <v>154</v>
+      </c>
+      <c r="AF31" s="4">
+        <v>11508</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A32">
+        <v>2019</v>
+      </c>
+      <c r="B32" s="4">
+        <v>11318</v>
+      </c>
+      <c r="C32">
+        <v>972</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2289</v>
+      </c>
+      <c r="E32" s="4">
+        <v>2277</v>
+      </c>
+      <c r="F32" s="5">
+        <f t="shared" ref="F32:F36" si="0">SUM(C32:E32)</f>
+        <v>5538</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1489</v>
+      </c>
+      <c r="H32">
+        <v>124</v>
+      </c>
+      <c r="I32" s="2">
+        <f t="shared" ref="I32:I36" si="1">SUM(G32:H32)</f>
+        <v>1613</v>
+      </c>
+      <c r="J32" s="4">
+        <v>18470</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L32" t="s">
+        <v>17</v>
+      </c>
+      <c r="V32" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z32" s="4">
+        <v>11318</v>
+      </c>
+      <c r="AA32">
+        <v>972</v>
+      </c>
+      <c r="AB32" s="4">
+        <v>2289</v>
+      </c>
+      <c r="AC32" s="4">
+        <v>2277</v>
+      </c>
+      <c r="AD32" s="4">
+        <v>1489</v>
+      </c>
+      <c r="AE32">
+        <v>124</v>
+      </c>
+      <c r="AF32" s="4">
+        <v>18470</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A33">
         <v>2020</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B33" s="4">
         <v>23222</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C33" s="4">
         <v>1232</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D33" s="4">
         <v>2703</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E33" s="4">
         <v>1913</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F33" s="5">
         <f t="shared" si="0"/>
         <v>5848</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G33" s="4">
         <v>1591</v>
       </c>
-      <c r="H32">
+      <c r="H33">
         <v>194</v>
       </c>
-      <c r="I32" s="2">
+      <c r="I33" s="2">
         <f t="shared" si="1"/>
         <v>1785</v>
       </c>
-      <c r="J32" s="5">
+      <c r="J33" s="4">
         <v>30855</v>
       </c>
-      <c r="K32" s="5" t="s">
+      <c r="K33" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L32" t="s">
+      <c r="L33" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33">
+      <c r="V33" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z33" s="4">
+        <v>23222</v>
+      </c>
+      <c r="AA33" s="4">
+        <v>1232</v>
+      </c>
+      <c r="AB33" s="4">
+        <v>2703</v>
+      </c>
+      <c r="AC33" s="4">
+        <v>1913</v>
+      </c>
+      <c r="AD33" s="4">
+        <v>1591</v>
+      </c>
+      <c r="AE33">
+        <v>194</v>
+      </c>
+      <c r="AF33" s="4">
+        <v>30855</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A34">
         <v>2021</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B34" s="4">
         <v>19707</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C34" s="4">
         <v>1418</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D34" s="4">
         <v>3146</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E34" s="4">
         <v>2042</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F34" s="5">
         <f t="shared" si="0"/>
         <v>6606</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G34" s="4">
         <v>2488</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H34" s="4">
         <v>1692</v>
       </c>
-      <c r="I33" s="2">
+      <c r="I34" s="2">
         <f t="shared" si="1"/>
         <v>4180</v>
       </c>
-      <c r="J33" s="5">
+      <c r="J34" s="4">
         <v>30494</v>
       </c>
-      <c r="K33" s="5" t="s">
+      <c r="K34" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L33" t="s">
+      <c r="L34" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34">
+      <c r="V34" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z34" s="4">
+        <v>19707</v>
+      </c>
+      <c r="AA34" s="4">
+        <v>1418</v>
+      </c>
+      <c r="AB34" s="4">
+        <v>3146</v>
+      </c>
+      <c r="AC34" s="4">
+        <v>2042</v>
+      </c>
+      <c r="AD34" s="4">
+        <v>2488</v>
+      </c>
+      <c r="AE34" s="4">
+        <v>1692</v>
+      </c>
+      <c r="AF34" s="4">
+        <v>30494</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A35">
         <v>2022</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B35" s="4">
         <v>29019</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C35" s="4">
         <v>2370</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D35" s="4">
         <v>2631</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E35" s="4">
         <v>3790</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F35" s="5">
         <f t="shared" si="0"/>
         <v>8791</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G35" s="4">
         <v>3606</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H35" s="4">
         <v>4124</v>
       </c>
-      <c r="I34" s="2">
+      <c r="I35" s="2">
         <f t="shared" si="1"/>
         <v>7730</v>
       </c>
-      <c r="J34" s="5">
+      <c r="J35" s="4">
         <v>45540</v>
       </c>
-      <c r="K34" s="5" t="s">
+      <c r="K35" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L34" t="s">
+      <c r="L35" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35">
+      <c r="V35" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z35" s="4">
+        <v>29019</v>
+      </c>
+      <c r="AA35" s="4">
+        <v>2370</v>
+      </c>
+      <c r="AB35" s="4">
+        <v>2631</v>
+      </c>
+      <c r="AC35" s="4">
+        <v>3790</v>
+      </c>
+      <c r="AD35" s="4">
+        <v>3606</v>
+      </c>
+      <c r="AE35" s="4">
+        <v>4124</v>
+      </c>
+      <c r="AF35" s="4">
+        <v>45540</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A36">
         <v>2023</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B36" s="4">
         <v>37604</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C36" s="4">
         <v>2191</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D36" s="4">
         <v>2579</v>
       </c>
-      <c r="E35">
+      <c r="E36">
         <v>471</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F36" s="5">
         <f t="shared" si="0"/>
         <v>5241</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G36" s="4">
         <v>3372</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H36" s="4">
         <v>2000</v>
       </c>
-      <c r="I35" s="2">
+      <c r="I36" s="2">
         <f t="shared" si="1"/>
         <v>5372</v>
       </c>
-      <c r="J35" s="5">
+      <c r="J36" s="4">
         <v>48218</v>
       </c>
-      <c r="K35" s="5" t="s">
+      <c r="K36" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L35" t="s">
+      <c r="L36" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36">
+      <c r="P36" s="8">
+        <v>0.21</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>0.36</v>
+      </c>
+      <c r="R36" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="S36" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="T36" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="U36" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="V36" t="s">
+        <v>26</v>
+      </c>
+      <c r="W36" t="s">
+        <v>19</v>
+      </c>
+      <c r="X36" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z36" s="4">
+        <v>37604</v>
+      </c>
+      <c r="AA36" s="4">
+        <v>2191</v>
+      </c>
+      <c r="AB36" s="4">
+        <v>2579</v>
+      </c>
+      <c r="AC36">
+        <v>471</v>
+      </c>
+      <c r="AD36" s="4">
+        <v>3372</v>
+      </c>
+      <c r="AE36" s="4">
+        <v>2000</v>
+      </c>
+      <c r="AF36" s="4">
+        <v>48218</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A37">
         <v>2024</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="7">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A38" s="6">
         <v>2025</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38">
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+    </row>
+    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A39">
         <v>2026</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A40">
         <v>2027</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A41">
         <v>2028</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A42">
         <v>2029</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A43">
         <v>2030</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A44">
         <v>2031</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A45">
         <v>2032</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A46">
         <v>2033</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A47">
         <v>2034</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A48">
         <v>2035</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>2036</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>2038</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>2039</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>2040</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>2041</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>2042</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>2044</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>2045</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>2046</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>2048</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>2049</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>2050</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>2051</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>2053</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>2054</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>2055</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>2057</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>2058</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>2059</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>2060</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>2062</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>2063</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>2064</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>2065</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>2066</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>2067</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>2068</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>2069</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>2070</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>2071</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>2072</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>2074</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>2075</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>2076</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>2077</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>2078</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>2081</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>2082</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>2084</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>2086</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>2087</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>2088</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>2089</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>2090</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>2091</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>2092</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>2093</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>2094</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>2095</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>2096</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109">
-        <v>2097</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110">
-        <v>2098</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111">
-        <v>2099</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A113">
         <v>2100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="G29:H29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PV_ICE/baselines/SupportingMaterial/Manual Files/inverter_Sector_deployment_inverterpm2.xlsx
+++ b/PV_ICE/baselines/SupportingMaterial/Manual Files/inverter_Sector_deployment_inverterpm2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\Manual Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063B8D61-9095-44DA-8508-2E3471BE23B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B00BAC0-6DFE-4863-9E07-23D130FB3C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B6A43E6F-DE9F-4A36-BCD0-E8AF60DFB633}"/>
+    <workbookView minimized="1" xWindow="1060" yWindow="1060" windowWidth="14400" windowHeight="8170" xr2:uid="{B6A43E6F-DE9F-4A36-BCD0-E8AF60DFB633}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -193,10 +193,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -770,18 +770,18 @@
       <c r="B29" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
       <c r="F29" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="7"/>
+      <c r="H29" s="8"/>
       <c r="I29" s="3" t="s">
         <v>8</v>
       </c>
@@ -1188,22 +1188,22 @@
       <c r="L36" t="s">
         <v>19</v>
       </c>
-      <c r="P36" s="8">
+      <c r="P36" s="7">
         <v>0.21</v>
       </c>
-      <c r="Q36" s="8">
+      <c r="Q36" s="7">
         <v>0.36</v>
       </c>
-      <c r="R36" s="8">
+      <c r="R36" s="7">
         <v>0.35</v>
       </c>
-      <c r="S36" s="8">
+      <c r="S36" s="7">
         <v>0.03</v>
       </c>
-      <c r="T36" s="8">
+      <c r="T36" s="7">
         <v>0.01</v>
       </c>
-      <c r="U36" s="8">
+      <c r="U36" s="7">
         <v>0.04</v>
       </c>
       <c r="V36" t="s">
